--- a/mensajes.xlsx
+++ b/mensajes.xlsx
@@ -1,43 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cardioinfantil-my.sharepoint.com/personal/kgonzalezt_lacardio_org/Documents/Escritorio/trabajos code/Front banco de sangre/Backend API/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_173BD0595AF008470462076A4042ACF17E14351A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8C5E325-2DF2-4B98-ACF4-313234BD4A35}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="27">
+  <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>mensaje</t>
+  </si>
+  <si>
+    <t>telefono</t>
+  </si>
+  <si>
+    <t>_x000D_
+Banco de Sangre Cardioinfantil:_x000D_
+Donar sangre es un acto solidario que puede salvar hasta 3 vidas._x000D_
+Te invitamos a donar y ayudar a quienes más lo necesitan.</t>
+  </si>
+  <si>
+    <t>3001234567</t>
+  </si>
+  <si>
+    <t>22/4/2026, 2:12:17 p. m.</t>
+  </si>
+  <si>
+    <t>"Esto es una prueba SMS desde la web Banco de Sangre"</t>
+  </si>
+  <si>
+    <t>3124973985</t>
+  </si>
+  <si>
+    <t>22/4/2026, 2:14:21 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 2:14:40 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 2:34:46 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 2:35:02 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 2:35:51 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 2:35:52 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 3:01:23 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 3:01:28 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 3:01:29 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 3:23:20 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 3:23:44 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 4:31:31 p. m.</t>
+  </si>
+  <si>
+    <t>"Esto es una prueba desde Postman con la documentación correcta."</t>
+  </si>
+  <si>
+    <t>22/4/2026, 4:34:57 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 4:35:00 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 4:35:42 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 4:37:26 p. m.</t>
+  </si>
+  <si>
+    <t>22/4/2026, 4:39:03 p. m.</t>
+  </si>
+  <si>
+    <t>correo</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -65,15 +160,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -397,260 +505,265 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>fecha</v>
-      </c>
-      <c r="B1" t="str">
-        <v>mensaje</v>
-      </c>
-      <c r="C1" t="str">
-        <v>telefono</v>
-      </c>
-    </row>
-    <row r="2" xml:space="preserve">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>46133</v>
       </c>
-      <c r="B2" t="str" xml:space="preserve">
-        <v xml:space="preserve">_x000d_
-Banco de Sangre Cardioinfantil:_x000d_
-Donar sangre es un acto solidario que puede salvar hasta 3 vidas._x000d_
-Te invitamos a donar y ayudar a quienes más lo necesitan.</v>
-      </c>
-      <c r="C2" t="str">
-        <v>3001234567</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>46133</v>
       </c>
-      <c r="B3" t="str" xml:space="preserve">
-        <v xml:space="preserve">_x000d_
-Banco de Sangre Cardioinfantil:_x000d_
-Donar sangre es un acto solidario que puede salvar hasta 3 vidas._x000d_
-Te invitamos a donar y ayudar a quienes más lo necesitan.</v>
+      <c r="B3" t="s">
+        <v>3</v>
       </c>
       <c r="C3">
         <v>3124973985</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>22/4/2026, 2:12:17 p. m.</v>
-      </c>
-      <c r="B4" t="str">
-        <v>"Esto es una prueba SMS desde la web Banco de Sangre"</v>
-      </c>
-      <c r="C4" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>22/4/2026, 2:14:21 p. m.</v>
-      </c>
-      <c r="B5" t="str">
-        <v>"Esto es una prueba SMS desde la web Banco de Sangre"</v>
-      </c>
-      <c r="C5" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>22/4/2026, 2:14:40 p. m.</v>
-      </c>
-      <c r="B6" t="str">
-        <v>"Esto es una prueba SMS desde la web Banco de Sangre"</v>
-      </c>
-      <c r="C6" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>22/4/2026, 2:34:46 p. m.</v>
-      </c>
-      <c r="B7" t="str">
-        <v>"Esto es una prueba SMS desde la web Banco de Sangre"</v>
-      </c>
-      <c r="C7" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>22/4/2026, 2:35:02 p. m.</v>
-      </c>
-      <c r="B8" t="str">
-        <v>"Esto es una prueba SMS desde la web Banco de Sangre"</v>
-      </c>
-      <c r="C8" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>22/4/2026, 2:35:51 p. m.</v>
-      </c>
-      <c r="B9" t="str">
-        <v>"Esto es una prueba SMS desde la web Banco de Sangre"</v>
-      </c>
-      <c r="C9" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>22/4/2026, 2:35:52 p. m.</v>
-      </c>
-      <c r="B10" t="str">
-        <v>"Esto es una prueba SMS desde la web Banco de Sangre"</v>
-      </c>
-      <c r="C10" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>22/4/2026, 3:01:23 p. m.</v>
-      </c>
-      <c r="B11" t="str">
-        <v>"Esto es una prueba SMS desde la web Banco de Sangre"</v>
-      </c>
-      <c r="C11" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>22/4/2026, 3:01:28 p. m.</v>
-      </c>
-      <c r="B12" t="str">
-        <v>"Esto es una prueba SMS desde la web Banco de Sangre"</v>
-      </c>
-      <c r="C12" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>22/4/2026, 3:01:28 p. m.</v>
-      </c>
-      <c r="B13" t="str">
-        <v>"Esto es una prueba SMS desde la web Banco de Sangre"</v>
-      </c>
-      <c r="C13" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>22/4/2026, 3:01:29 p. m.</v>
-      </c>
-      <c r="B14" t="str">
-        <v>"Esto es una prueba SMS desde la web Banco de Sangre"</v>
-      </c>
-      <c r="C14" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>22/4/2026, 3:23:20 p. m.</v>
-      </c>
-      <c r="B15" t="str">
-        <v>"Esto es una prueba SMS desde la web Banco de Sangre"</v>
-      </c>
-      <c r="C15" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>22/4/2026, 3:23:44 p. m.</v>
-      </c>
-      <c r="B16" t="str">
-        <v>"Esto es una prueba SMS desde la web Banco de Sangre"</v>
-      </c>
-      <c r="C16" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>22/4/2026, 4:31:31 p. m.</v>
-      </c>
-      <c r="B17" t="str">
-        <v>"Esto es una prueba desde Postman con la documentación correcta."</v>
-      </c>
-      <c r="C17" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>22/4/2026, 4:34:57 p. m.</v>
-      </c>
-      <c r="B18" t="str">
-        <v>"Esto es una prueba desde Postman con la documentación correcta."</v>
-      </c>
-      <c r="C18" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>22/4/2026, 4:35:00 p. m.</v>
-      </c>
-      <c r="B19" t="str">
-        <v>"Esto es una prueba desde Postman con la documentación correcta."</v>
-      </c>
-      <c r="C19" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>22/4/2026, 4:35:42 p. m.</v>
-      </c>
-      <c r="B20" t="str">
-        <v>"Esto es una prueba desde Postman con la documentación correcta."</v>
-      </c>
-      <c r="C20" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>22/4/2026, 4:37:26 p. m.</v>
-      </c>
-      <c r="B21" t="str">
-        <v>"Esto es una prueba desde Postman con la documentación correcta."</v>
-      </c>
-      <c r="C21" t="str">
-        <v>3124973985</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>22/4/2026, 4:39:03 p. m.</v>
-      </c>
-      <c r="B22" t="str">
-        <v>"Esto es una prueba desde Postman con la documentación correcta."</v>
-      </c>
-      <c r="C22" t="str">
-        <v>3124973985</v>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
+    <ignoredError sqref="A1:C22" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>